--- a/forms/trg/Formulir_TRG_ffbi.xlsx
+++ b/forms/trg/Formulir_TRG_ffbi.xlsx
@@ -916,7 +916,11 @@
           <t>Dr. Ir. Andi Hasizah, M.Sc.</t>
         </is>
       </c>
-      <c r="C5" s="12" t="n"/>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
       <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
@@ -947,7 +951,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="12" t="n"/>
@@ -980,7 +984,7 @@
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="12" t="n"/>
@@ -1013,7 +1017,7 @@
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="12" t="n"/>
@@ -1046,7 +1050,7 @@
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -1087,7 +1091,7 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
@@ -1128,7 +1132,7 @@
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D11" s="12" t="n"/>
@@ -1161,7 +1165,7 @@
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D12" s="12" t="n"/>
@@ -1190,7 +1194,7 @@
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D13" s="12" t="n"/>
@@ -1219,7 +1223,7 @@
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D14" s="12" t="n"/>
@@ -1248,11 +1252,15 @@
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D15" s="12" t="n"/>
-      <c r="E15" s="11" t="n"/>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>The Fermented Foods Beverage Innovation Research Group is dedicated to exploring the diverse world of food and beverage fermentation, a process that has been integral to human culture and nutrition for centuries.</t>
+        </is>
+      </c>
       <c r="F15" s="12" t="n"/>
       <c r="G15" s="12" t="n"/>
       <c r="H15" s="12" t="n"/>
